--- a/data/Blumenau/Maio 2025 - Cooper.xlsx
+++ b/data/Blumenau/Maio 2025 - Cooper.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bttom\OneDrive - FURB\Documentos\FURB\Projeto Cesta Básica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://furb-my.sharepoint.com/personal/bttomio_furb_br/Documents/Documentos/GitHub/CidadaniaFinanceira/data/Blumenau/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{AA9A18F1-C0E2-43AE-81FF-1AE3132F8E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9696DD1B-A050-4D95-9679-A829DC09C7D1}"/>
+  <xr:revisionPtr revIDLastSave="591" documentId="13_ncr:1_{AA9A18F1-C0E2-43AE-81FF-1AE3132F8E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BB3C83B-0C9C-4505-B3B3-E9ACDAB58CA0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
   <si>
     <t>MERCADO</t>
   </si>
@@ -48,9 +48,6 @@
     <t>DATA</t>
   </si>
   <si>
-    <t>10/05/2025</t>
-  </si>
-  <si>
     <t>Produto</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
     <t>Preço médio</t>
   </si>
   <si>
-    <t>0 = NÃO TINHA</t>
-  </si>
-  <si>
     <t>Arroz tipo 1</t>
   </si>
   <si>
@@ -87,9 +81,6 @@
     <t>Dalfovo</t>
   </si>
   <si>
-    <t>Kiarroz</t>
-  </si>
-  <si>
     <t>Urbano</t>
   </si>
   <si>
@@ -153,9 +144,6 @@
     <t>Batavo</t>
   </si>
   <si>
-    <t>Leco</t>
-  </si>
-  <si>
     <t>Tirol</t>
   </si>
   <si>
@@ -232,6 +220,9 @@
   </si>
   <si>
     <t>Prata</t>
+  </si>
+  <si>
+    <t>Maio/2025</t>
   </si>
 </sst>
 </file>
@@ -241,7 +232,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,91 +784,91 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1214,8 +1205,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L76"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I76"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -1233,7 +1224,7 @@
     <col min="14" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="18"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1244,7 +1235,7 @@
       <c r="H1" s="19"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -1255,7 +1246,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="25"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -1266,7 +1257,7 @@
       <c r="H3" s="23"/>
       <c r="I3" s="25"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5" thickBot="1">
+    <row r="4" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
@@ -1277,137 +1268,130 @@
       <c r="H4" s="27"/>
       <c r="I4" s="29"/>
     </row>
-    <row r="5" spans="1:12" ht="16.5" thickBot="1">
+    <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="43"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
+      <c r="E5" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
       <c r="H5" s="16"/>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" thickBot="1">
+    <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="B7" s="39" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="59" t="s">
+      <c r="C7" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="D7" s="41">
+        <v>1</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="F7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="54">
-        <v>1</v>
-      </c>
-      <c r="E7" s="32" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="59">
+        <f>AVERAGE(F8:H8)</f>
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="38"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="33" t="s">
         <v>15</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="36">
-        <f>AVERAGE(F8:H8)</f>
-        <v>3.4933333333333336</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="33" t="s">
-        <v>18</v>
       </c>
       <c r="F8" s="7">
         <v>5.29</v>
       </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
+      <c r="G8" s="7"/>
       <c r="H8" s="8">
         <v>5.19</v>
       </c>
-      <c r="I8" s="37"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="61" t="s">
+      <c r="I8" s="60"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="43">
+        <v>1</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="52">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34" t="s">
+      <c r="H9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="38">
+      <c r="I9" s="63">
         <f>AVERAGE(F10:H10)</f>
         <v>4.3233333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="53"/>
+    <row r="10" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="46"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="44"/>
       <c r="E10" s="35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F10" s="11">
         <v>4.6900000000000004</v>
@@ -1418,45 +1402,45 @@
       <c r="H10" s="12">
         <v>3.29</v>
       </c>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="59" t="s">
+      <c r="I10" s="64"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="36">
+      <c r="I11" s="59">
         <f>AVERAGE(F12:H12)</f>
         <v>35.596666666666664</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="55"/>
+    <row r="12" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="38"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="42"/>
       <c r="E12" s="33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F12" s="7">
         <v>30.99</v>
@@ -1467,45 +1451,45 @@
       <c r="H12" s="8">
         <v>35.9</v>
       </c>
-      <c r="I12" s="37"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="61" t="s">
+      <c r="I12" s="60"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="43">
+        <v>1</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="52">
-        <v>1</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="38">
+      <c r="I13" s="63">
         <f>AVERAGE(F14:H14)</f>
         <v>4.6566666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A14" s="62"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="53"/>
+    <row r="14" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="46"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="44"/>
       <c r="E14" s="35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F14" s="11">
         <v>4.3899999999999997</v>
@@ -1516,45 +1500,45 @@
       <c r="H14" s="12">
         <v>5.59</v>
       </c>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="54">
+      <c r="I14" s="64"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="41">
         <v>1</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="36">
+        <v>14</v>
+      </c>
+      <c r="I15" s="59">
         <f>AVERAGE(F16:H16)</f>
         <v>6.5233333333333334</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A16" s="60"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="55"/>
+    <row r="16" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F16" s="7">
         <v>5.99</v>
@@ -1565,94 +1549,90 @@
       <c r="H16" s="8">
         <v>6.79</v>
       </c>
-      <c r="I16" s="37"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="61" t="s">
+      <c r="I16" s="60"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="9"/>
+      <c r="H17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="38">
+      <c r="I17" s="63">
         <f>AVERAGE(F18:H18)</f>
-        <v>20.233333333333334</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A18" s="62"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="53"/>
+        <v>30.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="46"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="44"/>
       <c r="E18" s="35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F18" s="11">
         <v>27.8</v>
       </c>
-      <c r="G18" s="11">
-        <v>0</v>
-      </c>
+      <c r="G18" s="11"/>
       <c r="H18" s="12">
         <v>32.9</v>
       </c>
-      <c r="I18" s="39"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="59" t="s">
+      <c r="I18" s="64"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="41">
+        <v>0.9</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="H19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="54">
-        <v>0.9</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="36">
+      <c r="I19" s="59">
         <f>AVERAGE(F20:H20)</f>
         <v>7.2233333333333336</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A20" s="60"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="55"/>
+    <row r="20" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="38"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F20" s="7">
         <v>7.19</v>
@@ -1663,45 +1643,45 @@
       <c r="H20" s="8">
         <v>7.19</v>
       </c>
-      <c r="I20" s="37"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="61" t="s">
+      <c r="I20" s="60"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="43">
+        <v>1</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="52">
-        <v>1</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="38">
+      <c r="I21" s="63">
         <f>AVERAGE(F22:H22)</f>
         <v>40.126666666666665</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A22" s="62"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="53"/>
+    <row r="22" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="46"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="44"/>
       <c r="E22" s="35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F22" s="11">
         <v>37.979999999999997</v>
@@ -1712,84 +1692,84 @@
       <c r="H22" s="12">
         <v>40.5</v>
       </c>
-      <c r="I22" s="39"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="50" t="s">
+      <c r="I22" s="64"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="54">
+      <c r="B23" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="41">
         <v>1</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="6"/>
-      <c r="I23" s="36">
+      <c r="I23" s="59">
         <f>AVERAGE(F24:H24)</f>
         <v>13.9</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A24" s="60"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="55"/>
+    <row r="24" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="38"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F24" s="7">
         <v>13.9</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="37"/>
-    </row>
-    <row r="25" spans="1:9" ht="28.5">
-      <c r="A25" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="52">
+      <c r="I24" s="60"/>
+    </row>
+    <row r="25" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="43">
         <v>1</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" s="58" t="s">
-        <v>54</v>
+        <v>17</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>50</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H25" s="10"/>
-      <c r="I25" s="38">
+      <c r="I25" s="63">
         <f>AVERAGE(F26:H26)</f>
         <v>5.4350000000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A26" s="62"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="53"/>
+    <row r="26" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="46"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="44"/>
       <c r="E26" s="35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F26" s="11">
         <v>4.8899999999999997</v>
@@ -1798,86 +1778,86 @@
         <v>5.98</v>
       </c>
       <c r="H26" s="12"/>
-      <c r="I26" s="39"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="46">
+      <c r="I26" s="64"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="53">
         <v>1</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="6"/>
-      <c r="I27" s="36">
+      <c r="I27" s="59">
         <f>AVERAGE(F28:H28)</f>
         <v>9.98</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A28" s="64"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="47"/>
+    <row r="28" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="50"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="54"/>
       <c r="E28" s="33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F28" s="7">
         <v>9.98</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
-      <c r="I28" s="37"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="61" t="s">
+      <c r="I28" s="60"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="43">
+        <v>1</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="52">
-        <v>1</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="38">
+      <c r="I29" s="63">
         <f>AVERAGE(F30:H30)</f>
         <v>4.786666666666668</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A30" s="60"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="57"/>
+    <row r="30" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="38"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F30" s="13">
         <v>4.9800000000000004</v>
@@ -1888,43 +1868,43 @@
       <c r="H30" s="14">
         <v>4.6900000000000004</v>
       </c>
-      <c r="I30" s="39"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="46">
+      <c r="I30" s="64"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="53">
         <v>1</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H31" s="6"/>
-      <c r="I31" s="36">
+      <c r="I31" s="59">
         <f>AVERAGE(F32:H32)</f>
         <v>5.9350000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A32" s="64"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="47"/>
+    <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="50"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="54"/>
       <c r="E32" s="33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F32" s="7">
         <v>4.9800000000000004</v>
@@ -1933,89 +1913,67 @@
         <v>6.89</v>
       </c>
       <c r="H32" s="8"/>
-      <c r="I32" s="37"/>
-    </row>
-    <row r="35" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="36" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="37" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="38" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="39" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="40" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="41" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="42" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="43" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="44" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="45" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="46" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="47" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="48" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="49" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="50" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="51" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="52" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="53" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="54" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="55" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="56" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="57" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="58" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="59" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="60" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="61" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="62" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="63" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="64" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="65" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="66" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="67" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="68" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="69" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="70" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="71" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="72" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="73" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="74" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="75" ht="15.75" hidden="1" customHeight="1"/>
-    <row r="76" ht="15.75" hidden="1" customHeight="1"/>
+      <c r="I32" s="60"/>
+    </row>
+    <row r="35" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="E6:H6"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="D27:D28"/>
@@ -2032,21 +1990,43 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D21:D22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2058,7 +2038,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D87F49-2FE0-DA46-B88B-AA141AC8DB04}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
